--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20101-2023 artfynd.xlsx
+++ b/artfynd/A 20101-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136540462</v>
       </c>
       <c r="B2" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
